--- a/pages/shp/uploads/31-03-2026 - 31-03-2026.xlsx
+++ b/pages/shp/uploads/31-03-2026 - 31-03-2026.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3411" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3414" uniqueCount="512">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -1535,6 +1535,9 @@
   </si>
   <si>
     <t>30966</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
   </si>
   <si>
     <t>188173/PM/KPU.1/2026</t>
@@ -3349,7 +3352,7 @@
         <v>0.0</v>
       </c>
       <c r="BN10" t="n">
-        <v>1242.0</v>
+        <v>3726.0</v>
       </c>
       <c r="BO10" t="n">
         <v>0.0</v>
@@ -9794,21 +9797,18 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
-        <v>485</v>
-      </c>
-      <c r="C4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D4" t="s">
         <v>488</v>
-      </c>
-      <c r="D4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
         <v>485</v>
@@ -9822,7 +9822,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
         <v>485</v>
@@ -9836,7 +9836,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="B7" t="s">
         <v>485</v>
@@ -9850,7 +9850,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s">
         <v>485</v>
@@ -9864,7 +9864,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s">
         <v>485</v>
@@ -9878,7 +9878,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
         <v>485</v>
@@ -9892,7 +9892,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s">
         <v>485</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="B12" t="s">
         <v>485</v>
@@ -9920,7 +9920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s">
         <v>485</v>
@@ -9934,7 +9934,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s">
         <v>485</v>
@@ -9948,7 +9948,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B15" t="s">
         <v>485</v>
@@ -9962,7 +9962,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s">
         <v>485</v>
@@ -9976,7 +9976,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s">
         <v>485</v>
@@ -9990,7 +9990,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s">
         <v>485</v>
@@ -10004,7 +10004,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B19" t="s">
         <v>485</v>
@@ -10018,7 +10018,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s">
         <v>485</v>
@@ -10032,7 +10032,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B21" t="s">
         <v>485</v>
@@ -10046,7 +10046,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s">
         <v>485</v>
@@ -10060,7 +10060,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="B23" t="s">
         <v>485</v>
@@ -10074,7 +10074,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s">
         <v>485</v>
@@ -10088,7 +10088,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
         <v>485</v>
@@ -10102,7 +10102,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s">
         <v>485</v>
@@ -10111,6 +10111,20 @@
         <v>510</v>
       </c>
       <c r="D26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" t="s">
+        <v>485</v>
+      </c>
+      <c r="C27" t="s">
+        <v>511</v>
+      </c>
+      <c r="D27" t="s">
         <v>117</v>
       </c>
     </row>
